--- a/artfynd/A 1364-2026 artfynd.xlsx
+++ b/artfynd/A 1364-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132184715</v>
       </c>
       <c r="B2" t="n">
-        <v>58637</v>
+        <v>58640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1364-2026 artfynd.xlsx
+++ b/artfynd/A 1364-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132184715</v>
       </c>
       <c r="B2" t="n">
-        <v>58640</v>
+        <v>58641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 1364-2026 artfynd.xlsx
+++ b/artfynd/A 1364-2026 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>133889039</v>
       </c>
       <c r="B4" t="n">
-        <v>91910</v>
+        <v>91917</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 1364-2026 artfynd.xlsx
+++ b/artfynd/A 1364-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133312602</v>
+        <v>133889039</v>
       </c>
       <c r="B2" t="n">
-        <v>58658</v>
+        <v>91924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lugnets naturreservat, Lugnets naturreservat, Dlr</t>
+          <t>Lugnets Naturreservat , Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536396</v>
+        <v>536456</v>
       </c>
       <c r="R2" t="n">
-        <v>6722683</v>
+        <v>6722594</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,22 +743,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På undersidan av granlåga med hälften av barken kvar i fuktig kontinuitetgranskog. Låg så till att mittendelen var ca 10 cm ovan markskiktet. En del bark under hade lossat och jag tog en barkbit som hängde och fotograferade den ovanpå lågan. Tredje bilden är fotad hemma.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,6 +772,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,53 +791,51 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133826672</v>
+        <v>133881403</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>79397</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lugnets naturreservat, Lugnets naturreservat, Dlr</t>
+          <t>Lugnets naturreservat , Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536451</v>
+        <v>536322</v>
       </c>
       <c r="R3" t="n">
-        <v>6722592</v>
+        <v>6722722</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,27 +859,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack gamla,ej färsk kåda</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,69 +883,75 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133889039</v>
+        <v>133311991</v>
       </c>
       <c r="B4" t="n">
-        <v>91917</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lugnets Naturreservat , Dlr</t>
+          <t>Digertäktsgruvan, Digertäktsgruvan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536456</v>
+        <v>536313</v>
       </c>
       <c r="R4" t="n">
-        <v>6722594</v>
+        <v>6722593</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,27 +975,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På undersidan av granlåga med hälften av barken kvar i fuktig kontinuitetgranskog. Låg så till att mittendelen var ca 10 cm ovan markskiktet. En del bark under hade lossat och jag tog en barkbit som hängde och fotograferade den ovanpå lågan. Tredje bilden är fotad hemma.</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,7 +999,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1023,27 +1017,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133881143</v>
+        <v>133881073</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1062,14 +1056,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lugnets Naturreservat , Dlr</t>
+          <t>Lugnets naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536456</v>
+        <v>536544</v>
       </c>
       <c r="R5" t="n">
-        <v>6722594</v>
+        <v>6722592</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,27 +1090,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:42</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Det är inte mitt fynd men jag vill rapportera att jag sett det. Lugnets naturreservat är styvmoderligt behandlat med sin hänvisning till att bara skogsvårdslagen gäller.</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,27 +1132,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132184715</v>
+        <v>133826672</v>
       </c>
       <c r="B6" t="n">
-        <v>58658</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103044</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1172,19 +1161,24 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lugnets naturreservat, Lugnets naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>536526</v>
+        <v>536451</v>
       </c>
       <c r="R6" t="n">
-        <v>6722578</v>
+        <v>6722592</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,22 +1202,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack gamla,ej färsk kåda</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,22 +1237,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133881073</v>
+        <v>133881143</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,16 +1260,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1289,14 +1288,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lugnets naturreservat, Dlr</t>
+          <t>Lugnets Naturreservat , Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>536544</v>
+        <v>536456</v>
       </c>
       <c r="R7" t="n">
-        <v>6722592</v>
+        <v>6722594</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,22 +1322,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:59</t>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Det är inte mitt fynd men jag vill rapportera att jag sett det. Lugnets naturreservat är styvmoderligt behandlat med sin hänvisning till att bara skogsvårdslagen gäller.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,6 +1366,452 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132184715</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lugnets naturreservat, Lugnets naturreservat, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>536526</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6722578</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133312602</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lugnets naturreservat, Lugnets naturreservat, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>536396</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6722683</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133827580</v>
+      </c>
+      <c r="B10" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Jungfruberget, Jungfruberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>536576</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6722543</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133880911</v>
+      </c>
+      <c r="B11" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lugnets naturreeservat, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>536589</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6722580</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stora Kopparberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Område med äldre granar och vackra slingrande linneor (som såklart inte blommar än.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1364-2026 artfynd.xlsx
+++ b/artfynd/A 1364-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133889039</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133881403</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133311991</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1129,6 +1149,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133881073</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1246,6 +1271,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133826672</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1366,6 +1396,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133881143</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1473,6 +1508,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132184715</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1588,6 +1628,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133312602</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1695,6 +1740,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133827580</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1812,8 +1862,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133880911</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>